--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_tr_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_tr_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -725,7 +725,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -824,7 +824,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7907,7 +7907,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9710,7 +9710,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10377,7 +10377,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10852,7 +10852,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>21-08-2021 08:30</t>
+          <t>2021-08-21 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>27-05-2021 08:30</t>
+          <t>2021-05-27 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12182,7 +12182,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12843,7 +12843,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -13029,7 +13029,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>27-03-2021 08:30</t>
+          <t>2021-03-27 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13401,7 +13401,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14331,7 +14331,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14517,7 +14517,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16195,7 +16195,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16575,7 +16575,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17238,7 +17238,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17517,7 +17517,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18083,7 +18083,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18463,7 +18463,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18748,7 +18748,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19698,7 +19698,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20173,7 +20173,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="n">
@@ -20363,7 +20363,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="n">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20553,7 +20553,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20743,7 +20743,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>12-09-2021 08:30</t>
+          <t>2021-12-09 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21313,7 +21313,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>15-06-2021 08:30</t>
+          <t>2021-06-15 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -21883,7 +21883,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="n">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22263,7 +22263,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22356,7 +22356,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22542,7 +22542,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -22914,7 +22914,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23007,7 +23007,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23193,7 +23193,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23379,7 +23379,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23579,7 +23579,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -23769,7 +23769,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -23864,7 +23864,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24244,7 +24244,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24434,7 +24434,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24529,7 +24529,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24719,7 +24719,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -24818,7 +24818,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25299,7 +25299,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -25489,7 +25489,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25584,7 +25584,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -25679,7 +25679,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>11-09-2021 08:30</t>
+          <t>2021-11-09 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -25869,7 +25869,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -25964,7 +25964,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26152,7 +26152,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26245,7 +26245,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26338,7 +26338,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -26813,7 +26813,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -26908,7 +26908,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -27098,7 +27098,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27193,7 +27193,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27383,7 +27383,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27478,7 +27478,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="inlineStr"/>
@@ -27571,7 +27571,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="inlineStr"/>
@@ -27664,7 +27664,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -27757,7 +27757,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -27850,7 +27850,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -27943,7 +27943,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -28036,7 +28036,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28222,7 +28222,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="inlineStr"/>
@@ -28315,7 +28315,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28501,7 +28501,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -28687,7 +28687,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -28780,7 +28780,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -28873,7 +28873,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -28968,7 +28968,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -29063,7 +29063,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29253,7 +29253,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29348,7 +29348,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29538,7 +29538,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -29633,7 +29633,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -29728,7 +29728,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -29823,7 +29823,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -29918,7 +29918,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30013,7 +30013,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="inlineStr"/>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="inlineStr"/>
@@ -30199,7 +30199,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30292,7 +30292,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30385,7 +30385,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30478,7 +30478,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30571,7 +30571,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="n">
@@ -30666,7 +30666,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -30761,7 +30761,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31141,7 +31141,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31331,7 +31331,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31426,7 +31426,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -31521,7 +31521,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -31616,7 +31616,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="n">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="n">
@@ -31996,7 +31996,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="n">
@@ -32091,7 +32091,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="n">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="n">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="n">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="n">
@@ -32471,7 +32471,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="n">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="n">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="n">
@@ -32756,7 +32756,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="n">
@@ -32851,7 +32851,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -32944,7 +32944,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33037,7 +33037,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33130,7 +33130,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33223,7 +33223,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33316,7 +33316,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33409,7 +33409,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33502,7 +33502,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33595,7 +33595,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33688,7 +33688,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -33783,7 +33783,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -33878,7 +33878,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -33973,7 +33973,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34068,7 +34068,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34258,7 +34258,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34353,7 +34353,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34543,7 +34543,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34638,7 +34638,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -34733,7 +34733,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -34828,7 +34828,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -35113,7 +35113,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35303,7 +35303,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35398,7 +35398,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35493,7 +35493,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35588,7 +35588,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="n">
@@ -35683,7 +35683,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="n">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="n">
@@ -35873,7 +35873,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="n">
@@ -35968,7 +35968,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="n">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="n">
@@ -36158,7 +36158,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="n">
@@ -36443,7 +36443,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="n">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -36633,7 +36633,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -36728,7 +36728,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -36823,7 +36823,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -37013,7 +37013,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -37203,7 +37203,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37298,7 +37298,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37488,7 +37488,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37583,7 +37583,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -37678,7 +37678,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -37773,7 +37773,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -37868,7 +37868,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38058,7 +38058,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38153,7 +38153,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38248,7 +38248,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38343,7 +38343,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -38438,7 +38438,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -38533,7 +38533,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -38723,7 +38723,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>20-07-2021 08:30</t>
+          <t>2021-07-20 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -38913,7 +38913,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>21-08-2021 08:30</t>
+          <t>2021-08-21 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39008,7 +39008,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39103,7 +39103,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39198,7 +39198,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39293,7 +39293,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39388,7 +39388,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39487,7 +39487,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -39683,7 +39683,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -39778,7 +39778,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -39873,7 +39873,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="n">
@@ -39968,7 +39968,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>13-05-2021 08:30</t>
+          <t>2021-05-13 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40063,7 +40063,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40158,7 +40158,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40253,7 +40253,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>10-09-2021 08:30</t>
+          <t>2021-10-09 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="n">
@@ -40538,7 +40538,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="n">
@@ -40633,7 +40633,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -40728,7 +40728,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -40827,7 +40827,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -40926,7 +40926,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41027,7 +41027,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="n">
@@ -41227,7 +41227,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41328,7 +41328,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -41427,7 +41427,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="n">
@@ -41627,7 +41627,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -41728,7 +41728,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -41827,7 +41827,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="n">
@@ -41928,7 +41928,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="n">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="n">
@@ -42130,7 +42130,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="n">
@@ -42231,7 +42231,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="n">
@@ -42332,7 +42332,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="n">
@@ -42431,7 +42431,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -42532,7 +42532,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -42633,7 +42633,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="n">
@@ -42732,7 +42732,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="n">
@@ -42833,7 +42833,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="n">
@@ -42934,7 +42934,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="n">
@@ -43033,7 +43033,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="n">
@@ -43134,7 +43134,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -43235,7 +43235,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="n">
@@ -43336,7 +43336,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="n">
@@ -43435,7 +43435,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="n">
@@ -43536,7 +43536,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -43635,7 +43635,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -43734,7 +43734,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -43835,7 +43835,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -43936,7 +43936,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44037,7 +44037,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -44138,7 +44138,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -44239,7 +44239,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -44338,7 +44338,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -44439,7 +44439,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -44540,7 +44540,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -44641,7 +44641,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -44742,7 +44742,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -44841,7 +44841,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -44940,7 +44940,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -45041,7 +45041,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -45241,7 +45241,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
@@ -45340,7 +45340,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -45441,7 +45441,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -45542,7 +45542,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="n">
@@ -45643,7 +45643,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="n">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="n">
@@ -45845,7 +45845,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="n">
@@ -45944,7 +45944,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="n">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="n">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="n">
@@ -46247,7 +46247,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="n">
@@ -46348,7 +46348,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="n">
@@ -46447,7 +46447,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="n">
@@ -46546,7 +46546,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="n">
@@ -46647,7 +46647,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="n">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="n">
@@ -46849,7 +46849,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="n">
@@ -46950,7 +46950,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="n">
@@ -47049,7 +47049,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="n">
@@ -47150,7 +47150,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="n">
@@ -47249,7 +47249,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="n">
@@ -47348,7 +47348,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="n">
@@ -47449,7 +47449,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="n">
@@ -47548,7 +47548,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="n">
@@ -47649,7 +47649,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="n">
@@ -47748,7 +47748,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="n">
@@ -47849,7 +47849,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="n">
@@ -47948,7 +47948,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="n">
@@ -48049,7 +48049,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="n">
@@ -48148,7 +48148,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="n">
@@ -48247,7 +48247,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="n">
@@ -48346,7 +48346,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="n">
@@ -48445,7 +48445,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="n">
@@ -48544,7 +48544,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="n">
@@ -48645,7 +48645,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="n">
@@ -48746,7 +48746,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="n">
@@ -48847,7 +48847,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="n">
@@ -48946,7 +48946,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="n">
@@ -49045,7 +49045,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="n">
@@ -49144,7 +49144,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="n">
@@ -49245,7 +49245,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="n">
@@ -49344,7 +49344,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -49445,7 +49445,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49546,7 +49546,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="n">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="n">
@@ -49847,7 +49847,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="n">
@@ -49946,7 +49946,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="n">
@@ -50047,7 +50047,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="n">
@@ -50148,7 +50148,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="n">
@@ -50247,7 +50247,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="n">
@@ -50348,7 +50348,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="n">
@@ -50449,7 +50449,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="n">
@@ -50550,7 +50550,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="n">
@@ -50651,7 +50651,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="n">
@@ -50752,7 +50752,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="n">
